--- a/practice-files/day19-31-SQL速查表.xlsx
+++ b/practice-files/day19-31-SQL速查表.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQLZoo表结构" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="语法速查" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL执行顺序" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="思考题" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -73,6 +74,22 @@
       <color rgb="00E74C3C"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00E67E22"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="002E7D32"/>
+      <sz val="10.5"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -114,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -129,6 +146,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1522,4 +1544,70 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="80" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>📝 思考题（先自己想想，点左侧+号展开答案）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>思考题1: WHERE和HAVING的执行顺序？为什么"WHERE COUNT(*)&gt;10"会报错？</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1" outlineLevel="1">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>💡 答案: 执行顺序：FROM→WHERE→GROUP BY→HAVING→SELECT→ORDER BY→LIMIT。WHERE在分组前执行，那时COUNT(*)还没算出来，所以分组后的条件只能放HAVING里。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>思考题2: LEFT JOIN和INNER JOIN的区别？工作中哪个更常用？</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" hidden="1" outlineLevel="1">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>💡 答案: LEFT JOIN保留左表所有行，右表没匹配就填NULL（"所有用户，买没买过都保留"）；INNER JOIN只留两边都匹配的行。工作中90%用LEFT JOIN。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>思考题3: 窗口函数和GROUP BY最大的区别？</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" hidden="1" outlineLevel="1">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>💡 答案: GROUP BY把组内行合并成一行（原始明细丢失）；窗口函数保留所有原始行，只在每行旁边加一列计算结果（如组内排名）。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/practice-files/day19-31-SQL速查表.xlsx
+++ b/practice-files/day19-31-SQL速查表.xlsx
@@ -1537,7 +1537,7 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>💡 记忆口诀：FWGH SOL — From Where Group Having Select Order Limit</t>
+          <t>记忆口诀：FWGH SOL — From Where Group Having Select Order Limit</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
     <row r="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>📝 思考题（先自己想想，点左侧+号展开答案）</t>
+          <t>思考题（先自己想想，点左侧+号展开答案）</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
     <row r="3" hidden="1" outlineLevel="1">
       <c r="A3" s="14" t="inlineStr">
         <is>
-          <t>💡 答案: 执行顺序：FROM→WHERE→GROUP BY→HAVING→SELECT→ORDER BY→LIMIT。WHERE在分组前执行，那时COUNT(*)还没算出来，所以分组后的条件只能放HAVING里。</t>
+          <t>答案: 执行顺序：FROM→WHERE→GROUP BY→HAVING→SELECT→ORDER BY→LIMIT。WHERE在分组前执行，那时COUNT(*)还没算出来，所以分组后的条件只能放HAVING里。</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
     <row r="7" hidden="1" outlineLevel="1">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>💡 答案: LEFT JOIN保留左表所有行，右表没匹配就填NULL（"所有用户，买没买过都保留"）；INNER JOIN只留两边都匹配的行。工作中90%用LEFT JOIN。</t>
+          <t>答案: LEFT JOIN保留左表所有行，右表没匹配就填NULL（"所有用户，买没买过都保留"）；INNER JOIN只留两边都匹配的行。工作中90%用LEFT JOIN。</t>
         </is>
       </c>
     </row>
@@ -1603,7 +1603,7 @@
     <row r="11" hidden="1" outlineLevel="1">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>💡 答案: GROUP BY把组内行合并成一行（原始明细丢失）；窗口函数保留所有原始行，只在每行旁边加一列计算结果（如组内排名）。</t>
+          <t>答案: GROUP BY把组内行合并成一行（原始明细丢失）；窗口函数保留所有原始行，只在每行旁边加一列计算结果（如组内排名）。</t>
         </is>
       </c>
     </row>
